--- a/data/dividends_info_20260903.xlsx
+++ b/data/dividends_info_20260903.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44.01499938964844</v>
+        <v>44.02500152587891</v>
       </c>
       <c r="I2" t="n">
-        <v>0.204475749739909</v>
+        <v>0.2044292944478286</v>
       </c>
       <c r="J2" t="n">
         <v>193</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44.00500106811523</v>
+        <v>44.02500152587891</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2045222084205593</v>
+        <v>0.2044292944478286</v>
       </c>
       <c r="J6" t="n">
         <v>102</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.80500030517578</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="I8" t="n">
-        <v>1.134215486404743</v>
+        <v>1.131600976920603</v>
       </c>
       <c r="J8" t="n">
         <v>81</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.43000030517578</v>
+        <v>24.3700008392334</v>
       </c>
       <c r="I9" t="n">
-        <v>2.415063416413473</v>
+        <v>2.421009354460734</v>
       </c>
       <c r="J9" t="n">
         <v>81</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.800000190734863</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I10" t="n">
-        <v>3.44827574867131</v>
+        <v>3.430531777311974</v>
       </c>
       <c r="J10" t="n">
         <v>74</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.30000019073486</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I11" t="n">
-        <v>4.466019334774215</v>
+        <v>4.423077085314424</v>
       </c>
       <c r="J11" t="n">
         <v>53</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.349999904632568</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8163265412042129</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J12" t="n">
         <v>46</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.159999847412109</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7364341303044438</v>
+        <v>0.7307692575736874</v>
       </c>
       <c r="J15" t="n">
         <v>25</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.80999946594238</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="I16" t="n">
-        <v>1.13397734588867</v>
+        <v>1.131600976920603</v>
       </c>
       <c r="J16" t="n">
         <v>18</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.976999998092651</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="I17" t="n">
-        <v>2.883156300201914</v>
+        <v>2.878787851056303</v>
       </c>
       <c r="J17" t="n">
         <v>18</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>44.00500106811523</v>
+        <v>44.02500152587891</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2045222084205593</v>
+        <v>0.2044292944478286</v>
       </c>
       <c r="J18" t="n">
         <v>18</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>95.19999694824219</v>
+        <v>96.25</v>
       </c>
       <c r="I19" t="n">
-        <v>1.397058868313921</v>
+        <v>1.381818181818182</v>
       </c>
       <c r="J19" t="n">
         <v>18</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.260000228881836</v>
+        <v>6.320000171661377</v>
       </c>
       <c r="I20" t="n">
-        <v>4.792332093150517</v>
+        <v>4.746835314106284</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1486,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C296"/>
+  <dimension ref="A1:C306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1594,7 +1594,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1645,7 +1645,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1713,7 +1713,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1730,7 +1730,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1747,7 +1747,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1764,7 +1764,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1808,14 +1808,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1832,7 +1832,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1859,14 +1859,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1876,14 +1876,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1900,7 +1900,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1910,14 +1910,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1927,14 +1927,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1968,7 +1968,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2036,12 +2036,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2053,12 +2053,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2070,12 +2070,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2121,17 +2121,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2143,41 +2143,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2189,46 +2189,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2240,46 +2240,46 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2291,29 +2291,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2325,80 +2325,80 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MB Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2410,29 +2410,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2444,80 +2444,80 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2529,46 +2529,46 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>MB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2580,46 +2580,46 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2631,46 +2631,46 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2682,29 +2682,29 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2716,12 +2716,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2733,29 +2733,29 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2767,29 +2767,29 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2801,29 +2801,29 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2835,12 +2835,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2852,12 +2852,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2886,29 +2886,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2920,12 +2920,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2937,12 +2937,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2954,12 +2954,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENTERA</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2971,24 +2971,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3015,14 +3015,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3039,29 +3039,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3073,12 +3073,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3090,12 +3090,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3107,29 +3107,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>ENTERA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3141,29 +3141,29 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3175,29 +3175,29 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3226,7 +3226,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3243,7 +3243,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3260,7 +3260,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3294,7 +3294,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3311,7 +3311,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3328,7 +3328,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3338,14 +3338,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3362,7 +3362,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3372,36 +3372,36 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3413,29 +3413,29 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3447,12 +3447,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3464,12 +3464,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3498,12 +3498,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3515,12 +3515,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3532,12 +3532,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3549,7 +3549,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3566,7 +3566,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3583,7 +3583,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3593,14 +3593,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3610,14 +3610,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3651,7 +3651,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3661,14 +3661,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3719,12 +3719,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3736,12 +3736,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3753,29 +3753,29 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3804,12 +3804,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3821,12 +3821,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3838,12 +3838,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3855,12 +3855,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3872,7 +3872,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3889,7 +3889,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3906,7 +3906,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3923,7 +3923,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3940,7 +3940,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3991,7 +3991,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4001,14 +4001,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4025,7 +4025,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4042,7 +4042,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4059,7 +4059,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4076,7 +4076,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4103,14 +4103,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4144,7 +4144,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4161,7 +4161,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4178,7 +4178,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4188,14 +4188,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4205,14 +4205,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4222,14 +4222,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4239,14 +4239,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4263,7 +4263,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4280,7 +4280,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4290,14 +4290,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4324,14 +4324,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4341,36 +4341,36 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4399,12 +4399,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4416,12 +4416,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4433,12 +4433,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4450,12 +4450,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4467,46 +4467,46 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4535,7 +4535,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4569,7 +4569,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4586,7 +4586,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4620,7 +4620,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4654,7 +4654,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4688,7 +4688,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4705,7 +4705,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4722,7 +4722,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4739,7 +4739,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4756,7 +4756,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4773,7 +4773,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4790,7 +4790,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4858,7 +4858,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4875,7 +4875,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4885,14 +4885,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4909,7 +4909,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4926,7 +4926,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4960,7 +4960,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4977,7 +4977,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4994,7 +4994,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5062,7 +5062,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5079,7 +5079,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5096,7 +5096,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5113,7 +5113,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5164,7 +5164,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5181,7 +5181,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5191,14 +5191,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5215,7 +5215,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5232,7 +5232,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5249,7 +5249,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5283,7 +5283,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5300,7 +5300,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5317,7 +5317,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5334,7 +5334,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5351,12 +5351,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5368,12 +5368,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5385,12 +5385,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5402,12 +5402,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5419,12 +5419,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5436,12 +5436,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5453,12 +5453,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5470,12 +5470,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5487,12 +5487,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5504,12 +5504,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5538,7 +5538,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5555,7 +5555,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5582,14 +5582,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5623,7 +5623,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5640,7 +5640,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5657,7 +5657,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5674,7 +5674,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5691,7 +5691,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5725,7 +5725,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5742,7 +5742,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5759,7 +5759,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5776,7 +5776,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5786,14 +5786,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5810,7 +5810,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5827,7 +5827,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5844,7 +5844,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5861,7 +5861,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5878,7 +5878,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5929,7 +5929,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5939,14 +5939,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5980,7 +5980,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5997,7 +5997,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6014,7 +6014,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6099,7 +6099,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6133,7 +6133,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6150,7 +6150,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6184,7 +6184,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6201,7 +6201,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6218,7 +6218,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6235,7 +6235,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6252,7 +6252,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6279,14 +6279,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6320,7 +6320,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6337,7 +6337,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6371,7 +6371,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6388,7 +6388,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6405,7 +6405,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6439,7 +6439,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6473,49 +6473,219 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Reway Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Leone Film Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>KALEON S.P.A.</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Itway S.p.A.</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>IDNTT S.A.</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>HELYX INDUSTRIES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Gentili Mosconi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>LANDI RENZO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Renovalo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C306" t="inlineStr">
         <is>
           <t>SB Annual Report</t>
         </is>
@@ -6545,78 +6715,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WEBSOLUTE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>